--- a/test_export_2026-10-10.xlsx
+++ b/test_export_2026-10-10.xlsx
@@ -604,7 +604,7 @@
         <v>Export Date</v>
       </c>
       <c r="B3" t="str">
-        <v>10/10/2026, 3:14:39 PM</v>
+        <v>10/10/2026, 4:14:58 PM</v>
       </c>
     </row>
     <row r="4">
